--- a/results/0916-all/长江中游平原农业水产区/tech_selected_summary.xlsx
+++ b/results/0916-all/长江中游平原农业水产区/tech_selected_summary.xlsx
@@ -346,439 +346,439 @@
     <t>资阳区</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>技术55</t>
-  </si>
-  <si>
-    <t>技术56</t>
-  </si>
-  <si>
-    <t>技术57</t>
-  </si>
-  <si>
-    <t>技术58</t>
-  </si>
-  <si>
-    <t>技术59</t>
-  </si>
-  <si>
-    <t>技术60</t>
-  </si>
-  <si>
-    <t>技术61</t>
-  </si>
-  <si>
-    <t>技术62</t>
-  </si>
-  <si>
-    <t>技术63</t>
-  </si>
-  <si>
-    <t>技术64</t>
-  </si>
-  <si>
-    <t>技术65</t>
-  </si>
-  <si>
-    <t>技术66</t>
-  </si>
-  <si>
-    <t>技术67</t>
-  </si>
-  <si>
-    <t>技术68</t>
-  </si>
-  <si>
-    <t>技术69</t>
-  </si>
-  <si>
-    <t>技术70</t>
-  </si>
-  <si>
-    <t>技术71</t>
-  </si>
-  <si>
-    <t>技术72</t>
-  </si>
-  <si>
-    <t>技术73</t>
-  </si>
-  <si>
-    <t>技术74</t>
-  </si>
-  <si>
-    <t>技术75</t>
-  </si>
-  <si>
-    <t>技术76</t>
-  </si>
-  <si>
-    <t>技术77</t>
-  </si>
-  <si>
-    <t>技术78</t>
-  </si>
-  <si>
-    <t>技术79</t>
-  </si>
-  <si>
-    <t>技术80</t>
-  </si>
-  <si>
-    <t>技术81</t>
-  </si>
-  <si>
-    <t>技术82</t>
-  </si>
-  <si>
-    <t>技术83</t>
-  </si>
-  <si>
-    <t>技术84</t>
-  </si>
-  <si>
-    <t>技术85</t>
-  </si>
-  <si>
-    <t>技术86</t>
-  </si>
-  <si>
-    <t>技术87</t>
-  </si>
-  <si>
-    <t>技术88</t>
-  </si>
-  <si>
-    <t>技术89</t>
-  </si>
-  <si>
-    <t>技术90</t>
-  </si>
-  <si>
-    <t>技术91</t>
-  </si>
-  <si>
-    <t>技术92</t>
-  </si>
-  <si>
-    <t>技术93</t>
-  </si>
-  <si>
-    <t>技术94</t>
-  </si>
-  <si>
-    <t>技术95</t>
-  </si>
-  <si>
-    <t>技术96</t>
-  </si>
-  <si>
-    <t>技术97</t>
-  </si>
-  <si>
-    <t>技术98</t>
-  </si>
-  <si>
-    <t>技术99</t>
-  </si>
-  <si>
-    <t>技术100</t>
-  </si>
-  <si>
-    <t>技术101</t>
-  </si>
-  <si>
-    <t>技术102</t>
-  </si>
-  <si>
-    <t>技术103</t>
-  </si>
-  <si>
-    <t>技术104</t>
-  </si>
-  <si>
-    <t>技术105</t>
-  </si>
-  <si>
-    <t>技术106</t>
-  </si>
-  <si>
-    <t>技术107</t>
-  </si>
-  <si>
-    <t>技术108</t>
-  </si>
-  <si>
-    <t>技术109</t>
-  </si>
-  <si>
-    <t>技术110</t>
-  </si>
-  <si>
-    <t>技术111</t>
-  </si>
-  <si>
-    <t>技术112</t>
-  </si>
-  <si>
-    <t>技术113</t>
-  </si>
-  <si>
-    <t>技术114</t>
-  </si>
-  <si>
-    <t>技术115</t>
-  </si>
-  <si>
-    <t>技术116</t>
-  </si>
-  <si>
-    <t>技术117</t>
-  </si>
-  <si>
-    <t>技术118</t>
-  </si>
-  <si>
-    <t>技术119</t>
-  </si>
-  <si>
-    <t>技术120</t>
-  </si>
-  <si>
-    <t>技术121</t>
-  </si>
-  <si>
-    <t>技术122</t>
-  </si>
-  <si>
-    <t>技术123</t>
-  </si>
-  <si>
-    <t>技术124</t>
-  </si>
-  <si>
-    <t>技术125</t>
-  </si>
-  <si>
-    <t>技术126</t>
-  </si>
-  <si>
-    <t>技术127</t>
-  </si>
-  <si>
-    <t>技术128</t>
-  </si>
-  <si>
-    <t>技术129</t>
-  </si>
-  <si>
-    <t>技术130</t>
-  </si>
-  <si>
-    <t>技术131</t>
-  </si>
-  <si>
-    <t>技术132</t>
-  </si>
-  <si>
-    <t>技术133</t>
-  </si>
-  <si>
-    <t>技术134</t>
-  </si>
-  <si>
-    <t>技术135</t>
-  </si>
-  <si>
-    <t>技术136</t>
-  </si>
-  <si>
-    <t>技术137</t>
-  </si>
-  <si>
-    <t>技术138</t>
-  </si>
-  <si>
-    <t>技术139</t>
-  </si>
-  <si>
-    <t>技术140</t>
-  </si>
-  <si>
-    <t>技术141</t>
-  </si>
-  <si>
-    <t>技术142</t>
-  </si>
-  <si>
-    <t>技术143</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Tech55</t>
+  </si>
+  <si>
+    <t>Tech56</t>
+  </si>
+  <si>
+    <t>Tech57</t>
+  </si>
+  <si>
+    <t>Tech58</t>
+  </si>
+  <si>
+    <t>Tech59</t>
+  </si>
+  <si>
+    <t>Tech60</t>
+  </si>
+  <si>
+    <t>Tech61</t>
+  </si>
+  <si>
+    <t>Tech62</t>
+  </si>
+  <si>
+    <t>Tech63</t>
+  </si>
+  <si>
+    <t>Tech64</t>
+  </si>
+  <si>
+    <t>Tech65</t>
+  </si>
+  <si>
+    <t>Tech66</t>
+  </si>
+  <si>
+    <t>Tech67</t>
+  </si>
+  <si>
+    <t>Tech68</t>
+  </si>
+  <si>
+    <t>Tech69</t>
+  </si>
+  <si>
+    <t>Tech70</t>
+  </si>
+  <si>
+    <t>Tech71</t>
+  </si>
+  <si>
+    <t>Tech72</t>
+  </si>
+  <si>
+    <t>Tech73</t>
+  </si>
+  <si>
+    <t>Tech74</t>
+  </si>
+  <si>
+    <t>Tech75</t>
+  </si>
+  <si>
+    <t>Tech76</t>
+  </si>
+  <si>
+    <t>Tech77</t>
+  </si>
+  <si>
+    <t>Tech78</t>
+  </si>
+  <si>
+    <t>Tech79</t>
+  </si>
+  <si>
+    <t>Tech80</t>
+  </si>
+  <si>
+    <t>Tech81</t>
+  </si>
+  <si>
+    <t>Tech82</t>
+  </si>
+  <si>
+    <t>Tech83</t>
+  </si>
+  <si>
+    <t>Tech84</t>
+  </si>
+  <si>
+    <t>Tech85</t>
+  </si>
+  <si>
+    <t>Tech86</t>
+  </si>
+  <si>
+    <t>Tech87</t>
+  </si>
+  <si>
+    <t>Tech88</t>
+  </si>
+  <si>
+    <t>Tech89</t>
+  </si>
+  <si>
+    <t>Tech90</t>
+  </si>
+  <si>
+    <t>Tech91</t>
+  </si>
+  <si>
+    <t>Tech92</t>
+  </si>
+  <si>
+    <t>Tech93</t>
+  </si>
+  <si>
+    <t>Tech94</t>
+  </si>
+  <si>
+    <t>Tech95</t>
+  </si>
+  <si>
+    <t>Tech96</t>
+  </si>
+  <si>
+    <t>Tech97</t>
+  </si>
+  <si>
+    <t>Tech98</t>
+  </si>
+  <si>
+    <t>Tech99</t>
+  </si>
+  <si>
+    <t>Tech100</t>
+  </si>
+  <si>
+    <t>Tech101</t>
+  </si>
+  <si>
+    <t>Tech102</t>
+  </si>
+  <si>
+    <t>Tech103</t>
+  </si>
+  <si>
+    <t>Tech104</t>
+  </si>
+  <si>
+    <t>Tech105</t>
+  </si>
+  <si>
+    <t>Tech106</t>
+  </si>
+  <si>
+    <t>Tech107</t>
+  </si>
+  <si>
+    <t>Tech108</t>
+  </si>
+  <si>
+    <t>Tech109</t>
+  </si>
+  <si>
+    <t>Tech110</t>
+  </si>
+  <si>
+    <t>Tech111</t>
+  </si>
+  <si>
+    <t>Tech112</t>
+  </si>
+  <si>
+    <t>Tech113</t>
+  </si>
+  <si>
+    <t>Tech114</t>
+  </si>
+  <si>
+    <t>Tech115</t>
+  </si>
+  <si>
+    <t>Tech116</t>
+  </si>
+  <si>
+    <t>Tech117</t>
+  </si>
+  <si>
+    <t>Tech118</t>
+  </si>
+  <si>
+    <t>Tech119</t>
+  </si>
+  <si>
+    <t>Tech120</t>
+  </si>
+  <si>
+    <t>Tech121</t>
+  </si>
+  <si>
+    <t>Tech122</t>
+  </si>
+  <si>
+    <t>Tech123</t>
+  </si>
+  <si>
+    <t>Tech124</t>
+  </si>
+  <si>
+    <t>Tech125</t>
+  </si>
+  <si>
+    <t>Tech126</t>
+  </si>
+  <si>
+    <t>Tech127</t>
+  </si>
+  <si>
+    <t>Tech128</t>
+  </si>
+  <si>
+    <t>Tech129</t>
+  </si>
+  <si>
+    <t>Tech130</t>
+  </si>
+  <si>
+    <t>Tech131</t>
+  </si>
+  <si>
+    <t>Tech132</t>
+  </si>
+  <si>
+    <t>Tech133</t>
+  </si>
+  <si>
+    <t>Tech134</t>
+  </si>
+  <si>
+    <t>Tech135</t>
+  </si>
+  <si>
+    <t>Tech136</t>
+  </si>
+  <si>
+    <t>Tech137</t>
+  </si>
+  <si>
+    <t>Tech138</t>
+  </si>
+  <si>
+    <t>Tech139</t>
+  </si>
+  <si>
+    <t>Tech140</t>
+  </si>
+  <si>
+    <t>Tech141</t>
+  </si>
+  <si>
+    <t>Tech142</t>
+  </si>
+  <si>
+    <t>Tech143</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
@@ -925,10 +925,10 @@
     <t>irrigation (water-saving irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 543364204.26</t>
-  </si>
-  <si>
-    <t>总经济成本: 37291021.37</t>
+    <t>543364204.26</t>
+  </si>
+  <si>
+    <t>37291021.37</t>
   </si>
   <si>
     <t>Biochar_sheep &amp; goat</t>
@@ -955,7 +955,7 @@
     <t>4R(Right type)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 152042237.86</t>
+    <t>152042237.86</t>
   </si>
   <si>
     <t>Algae_sheep &amp; goat</t>
@@ -970,7 +970,7 @@
     <t>Physical additives_pig</t>
   </si>
   <si>
-    <t>总经济成本: 115644943.64</t>
+    <t>115644943.64</t>
   </si>
   <si>
     <t>Probiotics_beef cattle</t>
@@ -1012,10 +1012,10 @@
     <t>tillage management (zero tillage)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 127539129.97</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>127539129.97</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>Feedstock adjustment_beef cattle</t>
@@ -1024,7 +1024,7 @@
     <t>irrigation (drip irrigation)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 658731786.81</t>
+    <t>658731786.81</t>
   </si>
   <si>
     <t>Zeolite_pig</t>
@@ -1054,7 +1054,7 @@
     <t>irrigation (water-saving irrigation)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 2040464983.21</t>
+    <t>2040464983.21</t>
   </si>
   <si>
     <t>By-products source_sheep &amp; goat</t>
@@ -1066,7 +1066,7 @@
     <t>tillage management (zero tillage)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 140934809.38</t>
+    <t>140934809.38</t>
   </si>
   <si>
     <t>Probiotics_poultry</t>
@@ -1093,22 +1093,22 @@
     <t>EEF(DI)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 440084244.70</t>
-  </si>
-  <si>
-    <t>总经济成本: 449163277.65</t>
+    <t>440084244.70</t>
+  </si>
+  <si>
+    <t>449163277.65</t>
   </si>
   <si>
     <t>cover crop (mix)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 8718269.45</t>
-  </si>
-  <si>
-    <t>总经济成本: 264502116.07</t>
-  </si>
-  <si>
-    <t>总经济成本: 597960004.49</t>
+    <t>8718269.45</t>
+  </si>
+  <si>
+    <t>264502116.07</t>
+  </si>
+  <si>
+    <t>597960004.49</t>
   </si>
   <si>
     <t>Slatted floor vs Solid floor_beef cattle</t>
@@ -1132,13 +1132,13 @@
     <t>EEF(DI)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 1611914167.39</t>
-  </si>
-  <si>
-    <t>总经济成本: 596207979.92</t>
-  </si>
-  <si>
-    <t>总经济成本: 299272169.33</t>
+    <t>1611914167.39</t>
+  </si>
+  <si>
+    <t>596207979.92</t>
+  </si>
+  <si>
+    <t>299272169.33</t>
   </si>
   <si>
     <t>Frequent removal_sheep&amp;goat</t>
@@ -1147,28 +1147,28 @@
     <t>irrigation (water-saving irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 581659130.79</t>
-  </si>
-  <si>
-    <t>总经济成本: 96329854.39</t>
-  </si>
-  <si>
-    <t>总经济成本: 12030089.69</t>
+    <t>581659130.79</t>
+  </si>
+  <si>
+    <t>96329854.39</t>
+  </si>
+  <si>
+    <t>12030089.69</t>
   </si>
   <si>
     <t>cover crop (non-leguminous)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 92218882.19</t>
+    <t>92218882.19</t>
   </si>
   <si>
     <t>Yucca extract_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 480548260.88</t>
-  </si>
-  <si>
-    <t>总经济成本: 134948518.78</t>
+    <t>480548260.88</t>
+  </si>
+  <si>
+    <t>134948518.78</t>
   </si>
   <si>
     <t>Cover_poultry</t>
@@ -1177,28 +1177,28 @@
     <t>irrigation (water-saving irrigation)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 83042688.63</t>
+    <t>83042688.63</t>
   </si>
   <si>
     <t>compost（low）≤30%_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 160785142.15</t>
+    <t>160785142.15</t>
   </si>
   <si>
     <t>incorporation_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 1351978882.85</t>
-  </si>
-  <si>
-    <t>总经济成本: 147801600.70</t>
+    <t>1351978882.85</t>
+  </si>
+  <si>
+    <t>147801600.70</t>
   </si>
   <si>
     <t>nitrification inhibitor_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 272682713.89</t>
+    <t>272682713.89</t>
   </si>
   <si>
     <t>Low protein diet_Pig</t>
@@ -1219,67 +1219,67 @@
     <t>4R(Right place)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 244579755.32</t>
+    <t>244579755.32</t>
   </si>
   <si>
     <t>Feedstock adjustment_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 636705483.74</t>
+    <t>636705483.74</t>
   </si>
   <si>
     <t>By-products source_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 363834071.39</t>
+    <t>363834071.39</t>
   </si>
   <si>
     <t>Mixture additives _pig</t>
   </si>
   <si>
-    <t>总经济成本: 410228936.87</t>
-  </si>
-  <si>
-    <t>总经济成本: 23657197.45</t>
-  </si>
-  <si>
-    <t>总经济成本: 1263879.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 894041004.56</t>
-  </si>
-  <si>
-    <t>总经济成本: 34292885.20</t>
+    <t>410228936.87</t>
+  </si>
+  <si>
+    <t>23657197.45</t>
+  </si>
+  <si>
+    <t>1263879.00</t>
+  </si>
+  <si>
+    <t>894041004.56</t>
+  </si>
+  <si>
+    <t>34292885.20</t>
   </si>
   <si>
     <t>rolller press_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 538229285.02</t>
-  </si>
-  <si>
-    <t>总经济成本: 855661538.62</t>
+    <t>538229285.02</t>
+  </si>
+  <si>
+    <t>855661538.62</t>
   </si>
   <si>
     <t>irrigation (drip irrigation)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 282707561.63</t>
-  </si>
-  <si>
-    <t>总经济成本: 30490526.91</t>
-  </si>
-  <si>
-    <t>总经济成本: 301265135.95</t>
-  </si>
-  <si>
-    <t>总经济成本: 405853826.66</t>
+    <t>282707561.63</t>
+  </si>
+  <si>
+    <t>30490526.91</t>
+  </si>
+  <si>
+    <t>301265135.95</t>
+  </si>
+  <si>
+    <t>405853826.66</t>
   </si>
   <si>
     <t>anaerobic digestion_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 333227501.40</t>
+    <t>333227501.40</t>
   </si>
   <si>
     <t>Adsorbent_poultry</t>
@@ -1291,13 +1291,13 @@
     <t>tillage management (reduced tillage)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 752638670.73</t>
-  </si>
-  <si>
-    <t>总经济成本: 5454915.01</t>
-  </si>
-  <si>
-    <t>总经济成本: 22840837.22</t>
+    <t>752638670.73</t>
+  </si>
+  <si>
+    <t>5454915.01</t>
+  </si>
+  <si>
+    <t>22840837.22</t>
   </si>
   <si>
     <t>Feed processing_beef cattle</t>
@@ -1375,115 +1375,115 @@
     <t>4R(Right type)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 1836805151.79</t>
-  </si>
-  <si>
-    <t>总经济成本: 374722230.65</t>
-  </si>
-  <si>
-    <t>总经济成本: 17314488.86</t>
-  </si>
-  <si>
-    <t>总经济成本: 47473845.69</t>
-  </si>
-  <si>
-    <t>总经济成本: 96749554.97</t>
+    <t>1836805151.79</t>
+  </si>
+  <si>
+    <t>374722230.65</t>
+  </si>
+  <si>
+    <t>17314488.86</t>
+  </si>
+  <si>
+    <t>47473845.69</t>
+  </si>
+  <si>
+    <t>96749554.97</t>
   </si>
   <si>
     <t>4R(Right place)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 659683165.75</t>
-  </si>
-  <si>
-    <t>总经济成本: 254067673.78</t>
-  </si>
-  <si>
-    <t>总经济成本: 364039360.89</t>
-  </si>
-  <si>
-    <t>总经济成本: 412360034.91</t>
-  </si>
-  <si>
-    <t>总经济成本: 889378367.80</t>
-  </si>
-  <si>
-    <t>总经济成本: 336039523.44</t>
-  </si>
-  <si>
-    <t>总经济成本: 269131585.51</t>
-  </si>
-  <si>
-    <t>总经济成本: 4379651.43</t>
-  </si>
-  <si>
-    <t>总经济成本: 177044251.56</t>
-  </si>
-  <si>
-    <t>总经济成本: 160587124.14</t>
-  </si>
-  <si>
-    <t>总经济成本: 1258006644.09</t>
-  </si>
-  <si>
-    <t>总经济成本: 204933732.17</t>
-  </si>
-  <si>
-    <t>总经济成本: 124898863.01</t>
-  </si>
-  <si>
-    <t>总经济成本: 897458977.14</t>
+    <t>659683165.75</t>
+  </si>
+  <si>
+    <t>254067673.78</t>
+  </si>
+  <si>
+    <t>364039360.89</t>
+  </si>
+  <si>
+    <t>412360034.91</t>
+  </si>
+  <si>
+    <t>889378367.80</t>
+  </si>
+  <si>
+    <t>336039523.44</t>
+  </si>
+  <si>
+    <t>269131585.51</t>
+  </si>
+  <si>
+    <t>4379651.43</t>
+  </si>
+  <si>
+    <t>177044251.56</t>
+  </si>
+  <si>
+    <t>160587124.14</t>
+  </si>
+  <si>
+    <t>1258006644.09</t>
+  </si>
+  <si>
+    <t>204933732.17</t>
+  </si>
+  <si>
+    <t>124898863.01</t>
+  </si>
+  <si>
+    <t>897458977.14</t>
   </si>
   <si>
     <t>Urease Inhibitor_beef cattle</t>
   </si>
   <si>
-    <t>总经济成本: 527330204.84</t>
-  </si>
-  <si>
-    <t>总经济成本: 399032301.87</t>
-  </si>
-  <si>
-    <t>总经济成本: 199625808.60</t>
-  </si>
-  <si>
-    <t>总经济成本: 186762999.60</t>
-  </si>
-  <si>
-    <t>总经济成本: 386235359.55</t>
-  </si>
-  <si>
-    <t>总经济成本: 277686547.47</t>
-  </si>
-  <si>
-    <t>总经济成本: 984407297.47</t>
-  </si>
-  <si>
-    <t>总经济成本: 6926923.67</t>
-  </si>
-  <si>
-    <t>总经济成本: 150520461.15</t>
-  </si>
-  <si>
-    <t>总经济成本: 247485692.57</t>
+    <t>527330204.84</t>
+  </si>
+  <si>
+    <t>399032301.87</t>
+  </si>
+  <si>
+    <t>199625808.60</t>
+  </si>
+  <si>
+    <t>186762999.60</t>
+  </si>
+  <si>
+    <t>386235359.55</t>
+  </si>
+  <si>
+    <t>277686547.47</t>
+  </si>
+  <si>
+    <t>984407297.47</t>
+  </si>
+  <si>
+    <t>6926923.67</t>
+  </si>
+  <si>
+    <t>150520461.15</t>
+  </si>
+  <si>
+    <t>247485692.57</t>
   </si>
   <si>
     <t>4R(Right type)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 99729858.26</t>
+    <t>99729858.26</t>
   </si>
   <si>
     <t>manure（low）≤30%_friut</t>
   </si>
   <si>
-    <t>总经济成本: 514867530.76</t>
-  </si>
-  <si>
-    <t>总经济成本: 812158185.86</t>
-  </si>
-  <si>
-    <t>总经济成本: 542768260.26</t>
+    <t>514867530.76</t>
+  </si>
+  <si>
+    <t>812158185.86</t>
+  </si>
+  <si>
+    <t>542768260.26</t>
   </si>
   <si>
     <t>Probiotics_pig</t>
@@ -1492,7 +1492,7 @@
     <t>band application_pig</t>
   </si>
   <si>
-    <t>总经济成本: 731286442.03</t>
+    <t>731286442.03</t>
   </si>
 </sst>
 </file>
